--- a/docs/StructureDefinition-ImplantableDeviceDentalDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDentalDevice.xlsx
@@ -60,13 +60,13 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-17T15:32:01+00:00</t>
+    <t>2023-10-31T15:37:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>JPSys</t>
+    <t>VA</t>
   </si>
   <si>
     <t>Contact</t>

--- a/docs/StructureDefinition-ImplantableDeviceDentalDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDentalDevice.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31T15:37:13+00:00</t>
+    <t>2023-11-01T18:52:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for Use Case Implantable Device: Dental, ResourceType Device</t>
+    <t>This StructureDefinition contains the maps for VistA DENTAL DEVICE TRACKING (file 228.9) to FHIR Device</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-ImplantableDeviceDentalDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDentalDevice.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2897" uniqueCount="421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2896" uniqueCount="420">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-01T18:52:48+00:00</t>
+    <t>2023-11-08T21:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -760,10 +760,7 @@
     <t>This element is labeled as a modifier because the status contains the codes inactive and entered-in-error that mark the device (record)as not currently valid.</t>
   </si>
   <si>
-    <t>The availability status of the device.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/device-status|4.0.1</t>
+    <t>http://va.gov/fhir/ValueSet/VFDentalDeviceStatus</t>
   </si>
   <si>
     <t>.statusCode</t>
@@ -5151,11 +5148,9 @@
       <c r="X30" t="s" s="2">
         <v>127</v>
       </c>
-      <c r="Y30" t="s" s="2">
+      <c r="Y30" s="2"/>
+      <c r="Z30" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="Z30" t="s" s="2">
-        <v>233</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>37</v>
@@ -5188,27 +5183,27 @@
         <v>57</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="AL30" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="AL30" t="s" s="2">
+      <c r="AM30" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AN30" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="AM30" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AN30" t="s" s="2">
+      <c r="AO30" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="AO30" t="s" s="2">
-        <v>237</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5234,10 +5229,10 @@
         <v>133</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>239</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>240</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5267,11 +5262,11 @@
         <v>138</v>
       </c>
       <c r="Y31" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="Z31" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="Z31" t="s" s="2">
-        <v>242</v>
-      </c>
       <c r="AA31" t="s" s="2">
         <v>37</v>
       </c>
@@ -5288,7 +5283,7 @@
         <v>37</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>38</v>
@@ -5306,7 +5301,7 @@
         <v>37</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>37</v>
@@ -5320,14 +5315,14 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5349,13 +5344,13 @@
         <v>111</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5405,7 +5400,7 @@
         <v>37</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>38</v>
@@ -5420,27 +5415,27 @@
         <v>57</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>193</v>
       </c>
       <c r="AM32" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AN32" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="AN32" t="s" s="2">
+      <c r="AO32" t="s" s="2">
         <v>250</v>
-      </c>
-      <c r="AO32" t="s" s="2">
-        <v>251</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5466,10 +5461,10 @@
         <v>111</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>253</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>254</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5520,7 +5515,7 @@
         <v>37</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>38</v>
@@ -5535,7 +5530,7 @@
         <v>57</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>193</v>
@@ -5544,18 +5539,18 @@
         <v>88</v>
       </c>
       <c r="AN33" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="AO33" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="AO33" t="s" s="2">
-        <v>257</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5578,13 +5573,13 @@
         <v>37</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="M34" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>261</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5635,7 +5630,7 @@
         <v>37</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>38</v>
@@ -5650,27 +5645,27 @@
         <v>57</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>193</v>
       </c>
       <c r="AM34" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="AN34" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="AN34" t="s" s="2">
+      <c r="AO34" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="AO34" t="s" s="2">
-        <v>265</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5693,13 +5688,13 @@
         <v>37</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5750,7 +5745,7 @@
         <v>37</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>38</v>
@@ -5765,27 +5760,27 @@
         <v>57</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>193</v>
       </c>
       <c r="AM35" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="AN35" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="AN35" t="s" s="2">
+      <c r="AO35" t="s" s="2">
         <v>271</v>
-      </c>
-      <c r="AO35" t="s" s="2">
-        <v>272</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5811,10 +5806,10 @@
         <v>111</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>275</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5865,7 +5860,7 @@
         <v>37</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>38</v>
@@ -5880,27 +5875,27 @@
         <v>57</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>193</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AN36" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="AO36" t="s" s="2">
         <v>276</v>
-      </c>
-      <c r="AO36" t="s" s="2">
-        <v>277</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5926,13 +5921,13 @@
         <v>111</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>281</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5982,7 +5977,7 @@
         <v>37</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>38</v>
@@ -5997,7 +5992,7 @@
         <v>57</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>193</v>
@@ -6006,18 +6001,18 @@
         <v>37</v>
       </c>
       <c r="AN37" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="AO37" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="AO37" t="s" s="2">
-        <v>284</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6043,10 +6038,10 @@
         <v>176</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6097,7 +6092,7 @@
         <v>37</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>38</v>
@@ -6129,10 +6124,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6244,10 +6239,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6361,10 +6356,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6480,14 +6475,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6509,10 +6504,10 @@
         <v>111</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>293</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>294</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6563,7 +6558,7 @@
         <v>37</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>45</v>
@@ -6595,10 +6590,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6624,10 +6619,10 @@
         <v>65</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>296</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>297</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6657,11 +6652,11 @@
         <v>127</v>
       </c>
       <c r="Y43" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="Z43" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="Z43" t="s" s="2">
-        <v>299</v>
-      </c>
       <c r="AA43" t="s" s="2">
         <v>37</v>
       </c>
@@ -6678,7 +6673,7 @@
         <v>37</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>45</v>
@@ -6693,7 +6688,7 @@
         <v>57</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>193</v>
@@ -6710,10 +6705,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6739,10 +6734,10 @@
         <v>111</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>303</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6793,7 +6788,7 @@
         <v>37</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>38</v>
@@ -6808,7 +6803,7 @@
         <v>57</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>193</v>
@@ -6817,18 +6812,18 @@
         <v>37</v>
       </c>
       <c r="AN44" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AO44" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="AO44" t="s" s="2">
-        <v>306</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6854,13 +6849,13 @@
         <v>111</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="M45" t="s" s="2">
-        <v>309</v>
-      </c>
       <c r="N45" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -6910,7 +6905,7 @@
         <v>37</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>38</v>
@@ -6925,7 +6920,7 @@
         <v>57</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>193</v>
@@ -6942,10 +6937,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6971,10 +6966,10 @@
         <v>133</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7004,11 +6999,11 @@
         <v>138</v>
       </c>
       <c r="Y46" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="Z46" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="Z46" t="s" s="2">
-        <v>314</v>
-      </c>
       <c r="AA46" t="s" s="2">
         <v>37</v>
       </c>
@@ -7025,7 +7020,7 @@
         <v>37</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>38</v>
@@ -7057,10 +7052,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7172,10 +7167,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7289,10 +7284,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7315,19 +7310,19 @@
         <v>46</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="N49" t="s" s="2">
+      <c r="O49" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>322</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>37</v>
@@ -7376,7 +7371,7 @@
         <v>37</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>38</v>
@@ -7391,7 +7386,7 @@
         <v>57</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>37</v>
@@ -7408,10 +7403,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7437,16 +7432,16 @@
         <v>111</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="N50" t="s" s="2">
+      <c r="O50" t="s" s="2">
         <v>328</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>329</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>37</v>
@@ -7495,7 +7490,7 @@
         <v>37</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>38</v>
@@ -7510,27 +7505,27 @@
         <v>57</v>
       </c>
       <c r="AK50" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AN50" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="AL50" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AN50" t="s" s="2">
+      <c r="AO50" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="AO50" t="s" s="2">
-        <v>333</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7556,10 +7551,10 @@
         <v>176</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>336</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7610,7 +7605,7 @@
         <v>37</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>38</v>
@@ -7642,10 +7637,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7757,10 +7752,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7874,10 +7869,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7993,14 +7988,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8022,10 +8017,10 @@
         <v>133</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>342</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8076,7 +8071,7 @@
         <v>37</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>45</v>
@@ -8108,10 +8103,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8137,10 +8132,10 @@
         <v>111</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8191,7 +8186,7 @@
         <v>37</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>38</v>
@@ -8223,10 +8218,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8252,10 +8247,10 @@
         <v>176</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>347</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>348</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8306,7 +8301,7 @@
         <v>37</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>38</v>
@@ -8338,10 +8333,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8453,10 +8448,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8570,10 +8565,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8689,14 +8684,14 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -8718,10 +8713,10 @@
         <v>133</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>354</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8772,7 +8767,7 @@
         <v>37</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>38</v>
@@ -8804,10 +8799,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8833,10 +8828,10 @@
         <v>103</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8887,7 +8882,7 @@
         <v>37</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>38</v>
@@ -8919,10 +8914,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8948,10 +8943,10 @@
         <v>111</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9002,7 +8997,7 @@
         <v>37</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>45</v>
@@ -9034,10 +9029,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9063,10 +9058,10 @@
         <v>176</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9117,7 +9112,7 @@
         <v>37</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>38</v>
@@ -9149,10 +9144,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9264,10 +9259,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9381,10 +9376,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9500,10 +9495,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9529,10 +9524,10 @@
         <v>133</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>368</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>369</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -9583,7 +9578,7 @@
         <v>37</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>45</v>
@@ -9615,10 +9610,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9641,13 +9636,13 @@
         <v>37</v>
       </c>
       <c r="K69" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="L69" t="s" s="2">
         <v>371</v>
       </c>
-      <c r="L69" t="s" s="2">
+      <c r="M69" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>373</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -9698,7 +9693,7 @@
         <v>37</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>38</v>
@@ -9730,10 +9725,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9759,10 +9754,10 @@
         <v>133</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>376</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -9813,7 +9808,7 @@
         <v>37</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>38</v>
@@ -9845,10 +9840,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9871,17 +9866,17 @@
         <v>37</v>
       </c>
       <c r="K71" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="L71" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="L71" t="s" s="2">
+      <c r="M71" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>380</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>37</v>
@@ -9930,7 +9925,7 @@
         <v>37</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>38</v>
@@ -9945,27 +9940,27 @@
         <v>57</v>
       </c>
       <c r="AK71" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="AL71" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="AL71" t="s" s="2">
+      <c r="AM71" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AN71" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="AM71" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AN71" t="s" s="2">
+      <c r="AO71" t="s" s="2">
         <v>384</v>
-      </c>
-      <c r="AO71" t="s" s="2">
-        <v>385</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9991,10 +9986,10 @@
         <v>165</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="M72" t="s" s="2">
         <v>387</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>388</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10045,7 +10040,7 @@
         <v>37</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>38</v>
@@ -10060,10 +10055,10 @@
         <v>57</v>
       </c>
       <c r="AK72" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="AL72" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="AL72" t="s" s="2">
-        <v>390</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>37</v>
@@ -10077,10 +10072,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10103,16 +10098,16 @@
         <v>37</v>
       </c>
       <c r="K73" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="L73" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="L73" t="s" s="2">
+      <c r="M73" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="M73" t="s" s="2">
+      <c r="N73" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10162,7 +10157,7 @@
         <v>37</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>38</v>
@@ -10177,10 +10172,10 @@
         <v>57</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>37</v>
@@ -10194,10 +10189,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10220,17 +10215,17 @@
         <v>37</v>
       </c>
       <c r="K74" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="L74" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="L74" t="s" s="2">
+      <c r="M74" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>37</v>
@@ -10279,7 +10274,7 @@
         <v>37</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>38</v>
@@ -10294,10 +10289,10 @@
         <v>57</v>
       </c>
       <c r="AK74" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="AL74" t="s" s="2">
         <v>402</v>
-      </c>
-      <c r="AL74" t="s" s="2">
-        <v>403</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>37</v>
@@ -10311,10 +10306,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10340,13 +10335,13 @@
         <v>59</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="M75" t="s" s="2">
+      <c r="N75" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>407</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -10396,7 +10391,7 @@
         <v>37</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>38</v>
@@ -10411,10 +10406,10 @@
         <v>57</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>37</v>
@@ -10428,10 +10423,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10454,13 +10449,13 @@
         <v>37</v>
       </c>
       <c r="K76" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="L76" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="L76" t="s" s="2">
+      <c r="M76" t="s" s="2">
         <v>411</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>412</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -10511,7 +10506,7 @@
         <v>37</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>38</v>
@@ -10526,7 +10521,7 @@
         <v>57</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="AL76" t="s" s="2">
         <v>37</v>
@@ -10543,10 +10538,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10572,10 +10567,10 @@
         <v>133</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="M77" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>416</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -10626,7 +10621,7 @@
         <v>37</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>38</v>
@@ -10658,10 +10653,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10684,13 +10679,13 @@
         <v>37</v>
       </c>
       <c r="K78" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="L78" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="L78" t="s" s="2">
+      <c r="M78" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>420</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -10741,7 +10736,7 @@
         <v>37</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>38</v>

--- a/docs/StructureDefinition-ImplantableDeviceDentalDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDentalDevice.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-08T21:21:15+00:00</t>
+    <t>2023-11-08T21:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDentalDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDentalDevice.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-09T22:38:39+00:00</t>
+    <t>2023-11-14T14:54:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDentalDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDentalDevice.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T14:54:31+00:00</t>
+    <t>2023-11-14T17:25:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDentalDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDentalDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.0</t>
+    <t>0.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T17:25:19+00:00</t>
+    <t>2023-11-15T12:04:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -246,10 +246,10 @@
     <t>Mapping: UDI Mapping</t>
   </si>
   <si>
+    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
     <t>Mapping: Clinical Data Warehouse (CDW)</t>
-  </si>
-  <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
   </si>
   <si>
     <t/>
@@ -752,10 +752,10 @@
     <t>The device identifier (DI), a mandatory, fixed portion of a UDI that identifies the labeler and the specific version or model of a device.</t>
   </si>
   <si>
+    <t>1354: source value from DENTAL DEVICE TRACKING - UDI (#228.9-1)</t>
+  </si>
+  <si>
     <t>Dental.DeviceTracking.DeviceIdentification</t>
-  </si>
-  <si>
-    <t>1354: source value from DENTAL DEVICE TRACKING - UDI (#228.9-1)</t>
   </si>
   <si>
     <t>Device.udiCarrier.issuer</t>
@@ -892,10 +892,10 @@
     <t>FiveWs.status</t>
   </si>
   <si>
+    <t>1362: terminologyMaps using VF_DentalDeviceStatus on DENTAL DEVICE TRACKING - STATUS (#228.9-.08)</t>
+  </si>
+  <si>
     <t>Dental.DeviceTracking.DeviceStatus</t>
-  </si>
-  <si>
-    <t>1362: terminologyMaps using VF_DentalDeviceStatus on DENTAL DEVICE TRACKING - STATUS (#228.9-.08)</t>
   </si>
   <si>
     <t>Device.statusReason</t>
@@ -935,12 +935,12 @@
     <t>The lot or batch number within which a device was manufactured - which is a component of the production identifier (PI), a conditional, variable portion of a UDI.</t>
   </si>
   <si>
+    <t>1364: source value from DENTAL DEVICE TRACKING - DONATION ID (#228.9-4.8)</t>
+  </si>
+  <si>
     <t>Dental.DeviceTracking.DonationIdentification</t>
   </si>
   <si>
-    <t>1364: source value from DENTAL DEVICE TRACKING - DONATION ID (#228.9-4.8)</t>
-  </si>
-  <si>
     <t>Device.manufacturer</t>
   </si>
   <si>
@@ -953,10 +953,10 @@
     <t>.playedRole[typeCode=MANU].scoper.name</t>
   </si>
   <si>
+    <t>1370: source value from DENTAL DEVICE TRACKING - MANUFACTURER (#228.9-4.1)</t>
+  </si>
+  <si>
     <t>Dental.DeviceTracking.DeviceManufacturer</t>
-  </si>
-  <si>
-    <t>1370: source value from DENTAL DEVICE TRACKING - MANUFACTURER (#228.9-4.1)</t>
   </si>
   <si>
     <t>Device.manufactureDate</t>
@@ -978,12 +978,12 @@
     <t>The date a specific device was manufactured - which is a component of the production identifier (PI), a conditional, variable portion of a UDI.  For FHIR, The datetime syntax must converted to YYYY-MM-DD[THH:MM:SS].  If hour is present, the minutes and seconds should both be set to “00”.</t>
   </si>
   <si>
+    <t>1372: source value from DENTAL DEVICE TRACKING - MANUFACTURER DATE (#228.9-4.6)</t>
+  </si>
+  <si>
     <t>Dental.DeviceTracking.ManufacturerDate</t>
   </si>
   <si>
-    <t>1372: source value from DENTAL DEVICE TRACKING - MANUFACTURER DATE (#228.9-4.6)</t>
-  </si>
-  <si>
     <t>Device.expirationDate</t>
   </si>
   <si>
@@ -999,12 +999,12 @@
     <t>the expiration date of a specific device -  which is a component of the production identifier (PI), a conditional, variable portion of a UDI.  For FHIR, The datetime syntax must converted to YYYY-MM-DD[THH:MM:SS].  If hour is present, the minutes and seconds should both be set to “00”.</t>
   </si>
   <si>
+    <t>1375: source value from DENTAL DEVICE TRACKING - EXPRATION DATE (#228.9-4.7)</t>
+  </si>
+  <si>
     <t>Dental.DeviceTracking.ExpirationDate</t>
   </si>
   <si>
-    <t>1375: source value from DENTAL DEVICE TRACKING - EXPRATION DATE (#228.9-4.7)</t>
-  </si>
-  <si>
     <t>Device.lotNumber</t>
   </si>
   <si>
@@ -1014,12 +1014,12 @@
     <t>Lot number assigned by the manufacturer.</t>
   </si>
   <si>
+    <t>1378: source value from DENTAL DEVICE TRACKING - LOT (#228.9-4.4)</t>
+  </si>
+  <si>
     <t>Dental.DeviceTracking.DeviceLotNumber</t>
   </si>
   <si>
-    <t>1378: source value from DENTAL DEVICE TRACKING - LOT (#228.9-4.4)</t>
-  </si>
-  <si>
     <t>Device.serialNumber</t>
   </si>
   <si>
@@ -1035,10 +1035,10 @@
     <t>.playedRole[typeCode=MANU].id</t>
   </si>
   <si>
+    <t>1384: source value from DENTAL DEVICE TRACKING - S/N (#228.9-4.3)</t>
+  </si>
+  <si>
     <t>Dental.DeviceTracking.SerialNumber</t>
-  </si>
-  <si>
-    <t>1384: source value from DENTAL DEVICE TRACKING - S/N (#228.9-4.3)</t>
   </si>
   <si>
     <t>Device.deviceName</t>
@@ -1103,10 +1103,10 @@
     <t>.softwareName (included as part)</t>
   </si>
   <si>
+    <t>1392: source value from DENTAL DEVICE TRACKING - MODEL (#228.9-4.2)</t>
+  </si>
+  <si>
     <t>Dental.DeviceTracking.DeviceModel</t>
-  </si>
-  <si>
-    <t>1392: source value from DENTAL DEVICE TRACKING - MODEL (#228.9-4.2)</t>
   </si>
   <si>
     <t>Device.partNumber</t>
@@ -1185,10 +1185,10 @@
     <t>./originalText[mediaType/code="text/plain"]/data</t>
   </si>
   <si>
+    <t>1398: source value from DENTAL DEVICE TRACKING - TYPE (#228.9-2)</t>
+  </si>
+  <si>
     <t>Dental.DeviceTracking.DeviceType</t>
-  </si>
-  <si>
-    <t>1398: source value from DENTAL DEVICE TRACKING - TYPE (#228.9-2)</t>
   </si>
   <si>
     <t>Device.specialization</t>
@@ -1343,11 +1343,11 @@
     <t>FiveWs.subject</t>
   </si>
   <si>
+    <t>1403: reference from DENTAL DEVICE TRACKING - PATIENT (#228.9-.03)</t>
+  </si>
+  <si>
     <t>Dental.DeviceTracking.PatientIEN
 Dental.DeviceTrackingDetail.PatientIEN</t>
-  </si>
-  <si>
-    <t>1403: reference from DENTAL DEVICE TRACKING - PATIENT (#228.9-.03)</t>
   </si>
   <si>
     <t>Device.owner</t>
@@ -1814,8 +1814,8 @@
     <col min="37" max="37" width="102.6171875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="43.94140625" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="99.88671875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="99.88671875" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="43.94140625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3813,10 +3813,10 @@
         <v>78</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>78</v>
+        <v>198</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>198</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18" hidden="true">

--- a/docs/StructureDefinition-ImplantableDeviceDentalDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDentalDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.0</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T12:04:59+00:00</t>
+    <t>2023-11-15T19:14:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDentalDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDentalDevice.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T19:14:31+00:00</t>
+    <t>2023-11-15T20:37:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDentalDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDentalDevice.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T20:37:43+00:00</t>
+    <t>2023-11-29T20:32:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDentalDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDentalDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T20:32:59+00:00</t>
+    <t>2023-11-29T21:08:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDentalDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDentalDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T21:08:10+00:00</t>
+    <t>2023-12-12T19:04:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDentalDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDentalDevice.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$79</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$79</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2937" uniqueCount="461">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3016" uniqueCount="462">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-12T19:04:11+00:00</t>
+    <t>2023-12-21T07:51:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-implantable-device</t>
+    <t>http://va.gov/fhir/StructureDefinition/ImplantableDeviceDevice</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -1048,6 +1048,9 @@
   </si>
   <si>
     <t>This represents the manufacturer's name of the device as provided by the device, from a UDI label, or by a person describing the Device.  This typically would be used when a person provides the name(s) or when the device represents one of the names available from DeviceDefinition.</t>
+  </si>
+  <si>
+    <t>1386: target not supported</t>
   </si>
   <si>
     <t>Device.deviceName.id</t>
@@ -1773,7 +1776,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO79"/>
+  <dimension ref="A1:AP79"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="37.6015625" customWidth="true" bestFit="true"/>
@@ -1816,6 +1819,7 @@
     <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="99.88671875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="43.94140625" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="99.88671875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1942,6 +1946,9 @@
       <c r="AO1" t="s" s="1">
         <v>77</v>
       </c>
+      <c r="AP1" t="s" s="1">
+        <v>76</v>
+      </c>
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
@@ -2059,6 +2066,9 @@
       <c r="AO2" t="s" s="2">
         <v>78</v>
       </c>
+      <c r="AP2" t="s" s="2">
+        <v>78</v>
+      </c>
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
@@ -2176,6 +2186,9 @@
       <c r="AO3" t="s" s="2">
         <v>78</v>
       </c>
+      <c r="AP3" t="s" s="2">
+        <v>78</v>
+      </c>
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
@@ -2291,6 +2304,9 @@
       <c r="AO4" t="s" s="2">
         <v>78</v>
       </c>
+      <c r="AP4" t="s" s="2">
+        <v>78</v>
+      </c>
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
@@ -2408,6 +2424,9 @@
       <c r="AO5" t="s" s="2">
         <v>78</v>
       </c>
+      <c r="AP5" t="s" s="2">
+        <v>78</v>
+      </c>
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
@@ -2525,6 +2544,9 @@
       <c r="AO6" t="s" s="2">
         <v>78</v>
       </c>
+      <c r="AP6" t="s" s="2">
+        <v>78</v>
+      </c>
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
@@ -2642,6 +2664,9 @@
       <c r="AO7" t="s" s="2">
         <v>78</v>
       </c>
+      <c r="AP7" t="s" s="2">
+        <v>78</v>
+      </c>
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
@@ -2759,6 +2784,9 @@
       <c r="AO8" t="s" s="2">
         <v>78</v>
       </c>
+      <c r="AP8" t="s" s="2">
+        <v>78</v>
+      </c>
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
@@ -2876,6 +2904,9 @@
       <c r="AO9" t="s" s="2">
         <v>78</v>
       </c>
+      <c r="AP9" t="s" s="2">
+        <v>78</v>
+      </c>
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
@@ -2995,6 +3026,9 @@
       <c r="AO10" t="s" s="2">
         <v>78</v>
       </c>
+      <c r="AP10" t="s" s="2">
+        <v>78</v>
+      </c>
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
@@ -3112,6 +3146,9 @@
       <c r="AO11" t="s" s="2">
         <v>78</v>
       </c>
+      <c r="AP11" t="s" s="2">
+        <v>78</v>
+      </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
@@ -3227,6 +3264,9 @@
       <c r="AO12" t="s" s="2">
         <v>78</v>
       </c>
+      <c r="AP12" t="s" s="2">
+        <v>78</v>
+      </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
@@ -3344,6 +3384,9 @@
       <c r="AO13" t="s" s="2">
         <v>78</v>
       </c>
+      <c r="AP13" t="s" s="2">
+        <v>78</v>
+      </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
@@ -3463,6 +3506,9 @@
       <c r="AO14" t="s" s="2">
         <v>78</v>
       </c>
+      <c r="AP14" t="s" s="2">
+        <v>78</v>
+      </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
@@ -3582,6 +3628,9 @@
       <c r="AO15" t="s" s="2">
         <v>78</v>
       </c>
+      <c r="AP15" t="s" s="2">
+        <v>78</v>
+      </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
@@ -3701,6 +3750,9 @@
       <c r="AO16" t="s" s="2">
         <v>78</v>
       </c>
+      <c r="AP16" t="s" s="2">
+        <v>78</v>
+      </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
@@ -3818,6 +3870,9 @@
       <c r="AO17" t="s" s="2">
         <v>78</v>
       </c>
+      <c r="AP17" t="s" s="2">
+        <v>198</v>
+      </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
@@ -3933,6 +3988,9 @@
       <c r="AO18" t="s" s="2">
         <v>78</v>
       </c>
+      <c r="AP18" t="s" s="2">
+        <v>78</v>
+      </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
@@ -4050,6 +4108,9 @@
       <c r="AO19" t="s" s="2">
         <v>78</v>
       </c>
+      <c r="AP19" t="s" s="2">
+        <v>78</v>
+      </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
@@ -4165,6 +4226,9 @@
       <c r="AO20" t="s" s="2">
         <v>78</v>
       </c>
+      <c r="AP20" t="s" s="2">
+        <v>78</v>
+      </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
@@ -4282,6 +4346,9 @@
       <c r="AO21" t="s" s="2">
         <v>78</v>
       </c>
+      <c r="AP21" t="s" s="2">
+        <v>78</v>
+      </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
@@ -4397,6 +4464,9 @@
       <c r="AO22" t="s" s="2">
         <v>78</v>
       </c>
+      <c r="AP22" t="s" s="2">
+        <v>78</v>
+      </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
@@ -4514,6 +4584,9 @@
       <c r="AO23" t="s" s="2">
         <v>78</v>
       </c>
+      <c r="AP23" t="s" s="2">
+        <v>78</v>
+      </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
@@ -4633,6 +4706,9 @@
       <c r="AO24" t="s" s="2">
         <v>78</v>
       </c>
+      <c r="AP24" t="s" s="2">
+        <v>78</v>
+      </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
@@ -4748,6 +4824,9 @@
       <c r="AO25" t="s" s="2">
         <v>237</v>
       </c>
+      <c r="AP25" t="s" s="2">
+        <v>236</v>
+      </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
@@ -4863,6 +4942,9 @@
       <c r="AO26" t="s" s="2">
         <v>78</v>
       </c>
+      <c r="AP26" t="s" s="2">
+        <v>78</v>
+      </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
@@ -4980,6 +5062,9 @@
       <c r="AO27" t="s" s="2">
         <v>78</v>
       </c>
+      <c r="AP27" t="s" s="2">
+        <v>78</v>
+      </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
@@ -5097,6 +5182,9 @@
       <c r="AO28" t="s" s="2">
         <v>78</v>
       </c>
+      <c r="AP28" t="s" s="2">
+        <v>78</v>
+      </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
@@ -5214,6 +5302,9 @@
       <c r="AO29" t="s" s="2">
         <v>78</v>
       </c>
+      <c r="AP29" t="s" s="2">
+        <v>78</v>
+      </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
@@ -5331,6 +5422,9 @@
       <c r="AO30" t="s" s="2">
         <v>78</v>
       </c>
+      <c r="AP30" t="s" s="2">
+        <v>78</v>
+      </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
@@ -5446,6 +5540,9 @@
       <c r="AO31" t="s" s="2">
         <v>277</v>
       </c>
+      <c r="AP31" t="s" s="2">
+        <v>276</v>
+      </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
@@ -5561,6 +5658,9 @@
       <c r="AO32" t="s" s="2">
         <v>78</v>
       </c>
+      <c r="AP32" t="s" s="2">
+        <v>78</v>
+      </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
@@ -5678,6 +5778,9 @@
       <c r="AO33" t="s" s="2">
         <v>291</v>
       </c>
+      <c r="AP33" t="s" s="2">
+        <v>290</v>
+      </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
@@ -5793,6 +5896,9 @@
       <c r="AO34" t="s" s="2">
         <v>297</v>
       </c>
+      <c r="AP34" t="s" s="2">
+        <v>296</v>
+      </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
@@ -5908,6 +6014,9 @@
       <c r="AO35" t="s" s="2">
         <v>305</v>
       </c>
+      <c r="AP35" t="s" s="2">
+        <v>304</v>
+      </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
@@ -6023,6 +6132,9 @@
       <c r="AO36" t="s" s="2">
         <v>312</v>
       </c>
+      <c r="AP36" t="s" s="2">
+        <v>311</v>
+      </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
@@ -6138,6 +6250,9 @@
       <c r="AO37" t="s" s="2">
         <v>317</v>
       </c>
+      <c r="AP37" t="s" s="2">
+        <v>316</v>
+      </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
@@ -6255,6 +6370,9 @@
       <c r="AO38" t="s" s="2">
         <v>324</v>
       </c>
+      <c r="AP38" t="s" s="2">
+        <v>323</v>
+      </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
@@ -6365,18 +6483,21 @@
         <v>78</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>78</v>
+        <v>328</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>78</v>
+      </c>
+      <c r="AP39" t="s" s="2">
+        <v>328</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6485,13 +6606,16 @@
       <c r="AO40" t="s" s="2">
         <v>78</v>
       </c>
+      <c r="AP40" t="s" s="2">
+        <v>78</v>
+      </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6602,13 +6726,16 @@
       <c r="AO41" t="s" s="2">
         <v>78</v>
       </c>
+      <c r="AP41" t="s" s="2">
+        <v>78</v>
+      </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6721,17 +6848,20 @@
       <c r="AO42" t="s" s="2">
         <v>78</v>
       </c>
+      <c r="AP42" t="s" s="2">
+        <v>78</v>
+      </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6753,10 +6883,10 @@
         <v>152</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6807,7 +6937,7 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>86</v>
@@ -6834,15 +6964,18 @@
         <v>78</v>
       </c>
       <c r="AO43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AP43" t="s" s="2">
         <v>78</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6868,10 +7001,10 @@
         <v>106</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6901,10 +7034,10 @@
         <v>168</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>78</v>
@@ -6922,7 +7055,7 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>86</v>
@@ -6937,7 +7070,7 @@
         <v>98</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>234</v>
@@ -6949,15 +7082,18 @@
         <v>78</v>
       </c>
       <c r="AO44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AP44" t="s" s="2">
         <v>78</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6983,10 +7119,10 @@
         <v>152</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7037,7 +7173,7 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -7052,7 +7188,7 @@
         <v>98</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>234</v>
@@ -7061,18 +7197,21 @@
         <v>78</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AO45" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="AP45" t="s" s="2">
         <v>346</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7098,10 +7237,10 @@
         <v>152</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>321</v>
@@ -7154,7 +7293,7 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7181,15 +7320,18 @@
         <v>78</v>
       </c>
       <c r="AO46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AP46" t="s" s="2">
         <v>78</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7215,10 +7357,10 @@
         <v>174</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7248,10 +7390,10 @@
         <v>179</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>78</v>
@@ -7269,7 +7411,7 @@
         <v>78</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7296,15 +7438,18 @@
         <v>78</v>
       </c>
       <c r="AO47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AP47" t="s" s="2">
         <v>78</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7413,13 +7558,16 @@
       <c r="AO48" t="s" s="2">
         <v>78</v>
       </c>
+      <c r="AP48" t="s" s="2">
+        <v>78</v>
+      </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7530,13 +7678,16 @@
       <c r="AO49" t="s" s="2">
         <v>78</v>
       </c>
+      <c r="AP49" t="s" s="2">
+        <v>78</v>
+      </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7559,19 +7710,19 @@
         <v>87</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>78</v>
@@ -7620,7 +7771,7 @@
         <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -7635,7 +7786,7 @@
         <v>98</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>78</v>
@@ -7647,15 +7798,18 @@
         <v>78</v>
       </c>
       <c r="AO50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AP50" t="s" s="2">
         <v>78</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7681,16 +7835,16 @@
         <v>152</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>78</v>
@@ -7739,7 +7893,7 @@
         <v>78</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -7754,7 +7908,7 @@
         <v>98</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>78</v>
@@ -7763,18 +7917,21 @@
         <v>78</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AO51" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="AP51" t="s" s="2">
         <v>373</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7800,10 +7957,10 @@
         <v>217</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7854,7 +8011,7 @@
         <v>78</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -7881,15 +8038,18 @@
         <v>78</v>
       </c>
       <c r="AO52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AP52" t="s" s="2">
         <v>78</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7998,13 +8158,16 @@
       <c r="AO53" t="s" s="2">
         <v>78</v>
       </c>
+      <c r="AP53" t="s" s="2">
+        <v>78</v>
+      </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8115,13 +8278,16 @@
       <c r="AO54" t="s" s="2">
         <v>78</v>
       </c>
+      <c r="AP54" t="s" s="2">
+        <v>78</v>
+      </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8234,17 +8400,20 @@
       <c r="AO55" t="s" s="2">
         <v>78</v>
       </c>
+      <c r="AP55" t="s" s="2">
+        <v>78</v>
+      </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8266,10 +8435,10 @@
         <v>174</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8320,7 +8489,7 @@
         <v>78</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>86</v>
@@ -8347,15 +8516,18 @@
         <v>78</v>
       </c>
       <c r="AO56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AP56" t="s" s="2">
         <v>78</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8381,10 +8553,10 @@
         <v>152</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8435,7 +8607,7 @@
         <v>78</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8462,15 +8634,18 @@
         <v>78</v>
       </c>
       <c r="AO57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AP57" t="s" s="2">
         <v>78</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8496,10 +8671,10 @@
         <v>217</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8550,7 +8725,7 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8577,15 +8752,18 @@
         <v>78</v>
       </c>
       <c r="AO58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AP58" t="s" s="2">
         <v>78</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8694,13 +8872,16 @@
       <c r="AO59" t="s" s="2">
         <v>78</v>
       </c>
+      <c r="AP59" t="s" s="2">
+        <v>78</v>
+      </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8811,13 +8992,16 @@
       <c r="AO60" t="s" s="2">
         <v>78</v>
       </c>
+      <c r="AP60" t="s" s="2">
+        <v>78</v>
+      </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8930,17 +9114,20 @@
       <c r="AO61" t="s" s="2">
         <v>78</v>
       </c>
+      <c r="AP61" t="s" s="2">
+        <v>78</v>
+      </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -8962,10 +9149,10 @@
         <v>174</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9016,7 +9203,7 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -9043,15 +9230,18 @@
         <v>78</v>
       </c>
       <c r="AO62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AP62" t="s" s="2">
         <v>78</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9077,10 +9267,10 @@
         <v>144</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9131,7 +9321,7 @@
         <v>78</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9158,15 +9348,18 @@
         <v>78</v>
       </c>
       <c r="AO63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AP63" t="s" s="2">
         <v>78</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9192,10 +9385,10 @@
         <v>152</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9246,7 +9439,7 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>86</v>
@@ -9273,15 +9466,18 @@
         <v>78</v>
       </c>
       <c r="AO64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AP64" t="s" s="2">
         <v>78</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9307,10 +9503,10 @@
         <v>217</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9361,7 +9557,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9388,15 +9584,18 @@
         <v>78</v>
       </c>
       <c r="AO65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AP65" t="s" s="2">
         <v>78</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9505,13 +9704,16 @@
       <c r="AO66" t="s" s="2">
         <v>78</v>
       </c>
+      <c r="AP66" t="s" s="2">
+        <v>78</v>
+      </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9622,13 +9824,16 @@
       <c r="AO67" t="s" s="2">
         <v>78</v>
       </c>
+      <c r="AP67" t="s" s="2">
+        <v>78</v>
+      </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9741,13 +9946,16 @@
       <c r="AO68" t="s" s="2">
         <v>78</v>
       </c>
+      <c r="AP68" t="s" s="2">
+        <v>78</v>
+      </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9773,10 +9981,10 @@
         <v>174</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -9827,7 +10035,7 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>86</v>
@@ -9854,15 +10062,18 @@
         <v>78</v>
       </c>
       <c r="AO69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AP69" t="s" s="2">
         <v>78</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9885,13 +10096,13 @@
         <v>78</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -9942,7 +10153,7 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -9969,15 +10180,18 @@
         <v>78</v>
       </c>
       <c r="AO70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AP70" t="s" s="2">
         <v>78</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10003,10 +10217,10 @@
         <v>174</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10057,7 +10271,7 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10084,15 +10298,18 @@
         <v>78</v>
       </c>
       <c r="AO71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AP71" t="s" s="2">
         <v>78</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10115,17 +10332,17 @@
         <v>78</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>78</v>
@@ -10174,7 +10391,7 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10189,27 +10406,30 @@
         <v>98</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AO72" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="AP72" t="s" s="2">
         <v>425</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10235,10 +10455,10 @@
         <v>206</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10289,7 +10509,7 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10304,10 +10524,10 @@
         <v>98</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>78</v>
@@ -10316,15 +10536,18 @@
         <v>78</v>
       </c>
       <c r="AO73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AP73" t="s" s="2">
         <v>78</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10347,16 +10570,16 @@
         <v>78</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10406,7 +10629,7 @@
         <v>78</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10421,10 +10644,10 @@
         <v>98</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>78</v>
@@ -10433,15 +10656,18 @@
         <v>78</v>
       </c>
       <c r="AO74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AP74" t="s" s="2">
         <v>78</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10464,17 +10690,17 @@
         <v>78</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>78</v>
@@ -10523,7 +10749,7 @@
         <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -10538,10 +10764,10 @@
         <v>98</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>78</v>
@@ -10550,15 +10776,18 @@
         <v>78</v>
       </c>
       <c r="AO75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AP75" t="s" s="2">
         <v>78</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10584,13 +10813,13 @@
         <v>100</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -10640,7 +10869,7 @@
         <v>78</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
@@ -10655,10 +10884,10 @@
         <v>98</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>78</v>
@@ -10667,15 +10896,18 @@
         <v>78</v>
       </c>
       <c r="AO76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AP76" t="s" s="2">
         <v>78</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10698,13 +10930,13 @@
         <v>78</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -10755,7 +10987,7 @@
         <v>78</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -10770,7 +11002,7 @@
         <v>98</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AL77" t="s" s="2">
         <v>78</v>
@@ -10782,15 +11014,18 @@
         <v>78</v>
       </c>
       <c r="AO77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AP77" t="s" s="2">
         <v>78</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10816,10 +11051,10 @@
         <v>174</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -10870,7 +11105,7 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -10897,15 +11132,18 @@
         <v>78</v>
       </c>
       <c r="AO78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AP78" t="s" s="2">
         <v>78</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10928,13 +11166,13 @@
         <v>78</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -10985,7 +11223,7 @@
         <v>78</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -11014,9 +11252,12 @@
       <c r="AO79" t="s" s="2">
         <v>78</v>
       </c>
+      <c r="AP79" t="s" s="2">
+        <v>78</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO79">
+  <autoFilter ref="A1:AP79">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>

--- a/docs/StructureDefinition-ImplantableDeviceDentalDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDentalDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.10.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T07:51:53+00:00</t>
+    <t>2023-12-21T16:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDentalDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDentalDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.0</t>
+    <t>0.11.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T16:22:28+00:00</t>
+    <t>2023-12-28T09:08:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDentalDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDentalDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.11.0</t>
+    <t>0.12.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-28T09:08:39+00:00</t>
+    <t>2023-12-29T17:54:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDentalDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDentalDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.12.0</t>
+    <t>0.13.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-29T17:54:36+00:00</t>
+    <t>2024-01-03T19:41:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA DENTAL DEVICE TRACKING (file 228.9) to FHIR Device</t>
+    <t>This StructureDefinition contains the maps for VistA file DENTAL DEVICE TRACKING (#228.9) to ImplantableDeviceDevice</t>
   </si>
   <si>
     <t>Purpose</t>
